--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:38</t>
+    <t xml:space="preserve">2026-09-10 00:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:46</t>
+    <t xml:space="preserve">2026-09-18 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:56</t>
+    <t xml:space="preserve">2026-09-23 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:15</t>
+    <t xml:space="preserve">2026-10-02 15:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:29</t>
+    <t xml:space="preserve">2026-10-04 09:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:58</t>
+    <t xml:space="preserve">2026-10-05 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
